--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F940"/>
+  <dimension ref="A1:F941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22992,6 +22992,30 @@
         <v>216.56</v>
       </c>
       <c r="F940" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="C941" t="n">
+        <v>225.21</v>
+      </c>
+      <c r="D941" t="n">
+        <v>224.7</v>
+      </c>
+      <c r="E941" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="F941" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23008,7 +23032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1068"/>
+  <dimension ref="A1:B1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33691,6 +33715,16 @@
       </c>
       <c r="B1068" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -33853,28 +33887,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1617572148425526</v>
+        <v>0.1627386332264256</v>
       </c>
       <c r="J2" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K2" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08341671267215012</v>
+        <v>0.0844250628468316</v>
       </c>
       <c r="M2" t="n">
-        <v>3.360719591366948</v>
+        <v>3.362109669406469</v>
       </c>
       <c r="N2" t="n">
-        <v>16.00180843274848</v>
+        <v>16.00703616724848</v>
       </c>
       <c r="O2" t="n">
-        <v>4.000226047706364</v>
+        <v>4.000879424232687</v>
       </c>
       <c r="P2" t="n">
-        <v>213.918459718902</v>
+        <v>213.9084236765457</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33925,28 +33959,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.117454967264097</v>
+        <v>0.1180249937320086</v>
       </c>
       <c r="J3" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K3" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06486877359637777</v>
+        <v>0.06556459044430307</v>
       </c>
       <c r="M3" t="n">
-        <v>2.902651782726403</v>
+        <v>2.902483217095546</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06885073584911</v>
+        <v>11.06458173207163</v>
       </c>
       <c r="O3" t="n">
-        <v>3.326988238008831</v>
+        <v>3.326346604320065</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4484590169825</v>
+        <v>219.4426298926557</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33997,28 +34031,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1119162613805253</v>
+        <v>0.1119336762972921</v>
       </c>
       <c r="J4" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K4" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05669276971024872</v>
+        <v>0.05683841685787672</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95374639658238</v>
+        <v>2.950689995741091</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59937952964982</v>
+        <v>11.58704677039536</v>
       </c>
       <c r="O4" t="n">
-        <v>3.405786183783389</v>
+        <v>3.403975142446749</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6621392900079</v>
+        <v>221.6619612040405</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34069,28 +34103,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01928088574659356</v>
+        <v>0.01903287061354658</v>
       </c>
       <c r="J5" t="n">
+        <v>940</v>
+      </c>
+      <c r="K5" t="n">
         <v>939</v>
       </c>
-      <c r="K5" t="n">
-        <v>938</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.002168468819224723</v>
+        <v>0.002117937320327168</v>
       </c>
       <c r="M5" t="n">
-        <v>2.539679610996604</v>
+        <v>2.53836582149105</v>
       </c>
       <c r="N5" t="n">
-        <v>9.489043720890873</v>
+        <v>9.480352311149691</v>
       </c>
       <c r="O5" t="n">
-        <v>3.080429145572232</v>
+        <v>3.07901807580756</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6653345966699</v>
+        <v>216.667877180525</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34128,7 +34162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F940"/>
+  <dimension ref="A1:F941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64207,6 +64241,38 @@
         </is>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>-41.02686008584893,173.02003741791924</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>-41.02621278335081,173.01961811897777</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>-41.02557810597521,173.0191757883442</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>-41.02500512135477,173.01885155607502</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F941"/>
+  <dimension ref="A1:F943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23016,6 +23016,54 @@
         <v>216.02</v>
       </c>
       <c r="F941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="C942" t="n">
+        <v>224.94</v>
+      </c>
+      <c r="D942" t="n">
+        <v>224.13</v>
+      </c>
+      <c r="E942" t="n">
+        <v>215.8</v>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>222.28</v>
+      </c>
+      <c r="C943" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="D943" t="n">
+        <v>223.13</v>
+      </c>
+      <c r="E943" t="n">
+        <v>215.22</v>
+      </c>
+      <c r="F943" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23032,7 +23080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1069"/>
+  <dimension ref="A1:B1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33725,6 +33773,26 @@
       </c>
       <c r="B1069" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -33887,28 +33955,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1627386332264256</v>
+        <v>0.164542628930443</v>
       </c>
       <c r="J2" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K2" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0844250628468316</v>
+        <v>0.08633847770588832</v>
       </c>
       <c r="M2" t="n">
-        <v>3.362109669406469</v>
+        <v>3.36408026641093</v>
       </c>
       <c r="N2" t="n">
-        <v>16.00703616724848</v>
+        <v>16.01079164485119</v>
       </c>
       <c r="O2" t="n">
-        <v>4.000879424232687</v>
+        <v>4.001348728222921</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9084236765457</v>
+        <v>213.8899500938926</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33959,28 +34027,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1180249937320086</v>
+        <v>0.1188694614027495</v>
       </c>
       <c r="J3" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K3" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06556459044430307</v>
+        <v>0.06669442100504586</v>
       </c>
       <c r="M3" t="n">
-        <v>2.902483217095546</v>
+        <v>2.90062459709847</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06458173207163</v>
+        <v>11.04968605153651</v>
       </c>
       <c r="O3" t="n">
-        <v>3.326346604320065</v>
+        <v>3.324106805073584</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4426298926557</v>
+        <v>219.4339828982656</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34031,28 +34099,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1119336762972921</v>
+        <v>0.1115111686874649</v>
       </c>
       <c r="J4" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K4" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05683841685787672</v>
+        <v>0.05667921671618814</v>
       </c>
       <c r="M4" t="n">
-        <v>2.950689995741091</v>
+        <v>2.946526589307026</v>
       </c>
       <c r="N4" t="n">
-        <v>11.58704677039536</v>
+        <v>11.56504406141767</v>
       </c>
       <c r="O4" t="n">
-        <v>3.403975142446749</v>
+        <v>3.400741692839618</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6619612040405</v>
+        <v>221.6662889538158</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34103,28 +34171,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01903287061354658</v>
+        <v>0.01832129459325323</v>
       </c>
       <c r="J5" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="K5" t="n">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002117937320327168</v>
+        <v>0.001971056237952462</v>
       </c>
       <c r="M5" t="n">
-        <v>2.53836582149105</v>
+        <v>2.536941401161639</v>
       </c>
       <c r="N5" t="n">
-        <v>9.480352311149691</v>
+        <v>9.466214558323234</v>
       </c>
       <c r="O5" t="n">
-        <v>3.07901807580756</v>
+        <v>3.076721397579449</v>
       </c>
       <c r="P5" t="n">
-        <v>216.667877180525</v>
+        <v>216.6751829776919</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34162,7 +34230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F941"/>
+  <dimension ref="A1:F943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64273,6 +64341,70 @@
         </is>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>-41.026860801942384,173.02003563043624</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>-41.02621392066548,173.01961528005478</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>-41.02558044620528,173.0191697533545</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>-41.02500512132143,173.01884893920007</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>-41.02686214988291,173.0200322657623</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>-41.02621724836355,173.01960697357578</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>-41.02558455187131,173.01915916565218</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>-41.02500512123325,173.01884204016613</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F943"/>
+  <dimension ref="A1:F946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23064,6 +23064,78 @@
         <v>215.22</v>
       </c>
       <c r="F943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>222.15</v>
+      </c>
+      <c r="C944" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="D944" t="n">
+        <v>222.32</v>
+      </c>
+      <c r="E944" t="n">
+        <v>214.57</v>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="C945" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="D945" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="E945" t="n">
+        <v>214.59</v>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>221.63</v>
+      </c>
+      <c r="C946" t="n">
+        <v>223.18</v>
+      </c>
+      <c r="D946" t="n">
+        <v>222.23</v>
+      </c>
+      <c r="E946" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="F946" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23080,7 +23152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1071"/>
+  <dimension ref="A1:B1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33793,6 +33865,36 @@
       </c>
       <c r="B1071" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -33955,28 +34057,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.164542628930443</v>
+        <v>0.1668602274841363</v>
       </c>
       <c r="J2" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K2" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08633847770588832</v>
+        <v>0.08894433994475248</v>
       </c>
       <c r="M2" t="n">
-        <v>3.36408026641093</v>
+        <v>3.365144818909067</v>
       </c>
       <c r="N2" t="n">
-        <v>16.01079164485119</v>
+        <v>16.001672099895</v>
       </c>
       <c r="O2" t="n">
-        <v>4.001348728222921</v>
+        <v>4.000209007026383</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8899500938926</v>
+        <v>213.8661483941938</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34027,28 +34129,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1188694614027495</v>
+        <v>0.1193457409547001</v>
       </c>
       <c r="J3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06669442100504586</v>
+        <v>0.06763802362948934</v>
       </c>
       <c r="M3" t="n">
-        <v>2.90062459709847</v>
+        <v>2.893821504895812</v>
       </c>
       <c r="N3" t="n">
-        <v>11.04968605153651</v>
+        <v>11.01642304442266</v>
       </c>
       <c r="O3" t="n">
-        <v>3.324106805073584</v>
+        <v>3.319099734027686</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4339828982656</v>
+        <v>219.4290922168425</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34099,28 +34201,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1115111686874649</v>
+        <v>0.110041705451259</v>
       </c>
       <c r="J4" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K4" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05667921671618814</v>
+        <v>0.05557984437837649</v>
       </c>
       <c r="M4" t="n">
-        <v>2.946526589307026</v>
+        <v>2.944438450326324</v>
       </c>
       <c r="N4" t="n">
-        <v>11.56504406141767</v>
+        <v>11.54504568797386</v>
       </c>
       <c r="O4" t="n">
-        <v>3.400741692839618</v>
+        <v>3.397800124782777</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6662889538158</v>
+        <v>221.6813816014607</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34171,28 +34273,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01832129459325323</v>
+        <v>0.0166718105859321</v>
       </c>
       <c r="J5" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="K5" t="n">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001971056237952462</v>
+        <v>0.001640880403046219</v>
       </c>
       <c r="M5" t="n">
-        <v>2.536941401161639</v>
+        <v>2.538035597444958</v>
       </c>
       <c r="N5" t="n">
-        <v>9.466214558323234</v>
+        <v>9.457074088020464</v>
       </c>
       <c r="O5" t="n">
-        <v>3.076721397579449</v>
+        <v>3.075235615041629</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6751829776919</v>
+        <v>216.6921666101303</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34230,7 +34332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F943"/>
+  <dimension ref="A1:F946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64405,6 +64507,102 @@
         </is>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>-41.02686269748372,173.02003089886344</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>-41.02621998634252,173.0196001391304</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>-41.02558787746008,173.01915058961234</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>-41.02500512113392,173.01883430849017</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>-41.02686375056216,173.02002827021178</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>-41.026220744552006,173.01959824651465</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>-41.02558754900689,173.01915143662865</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>-41.02500512113699,173.0188345463879</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>-41.02686488788682,173.02002543126787</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>-41.026221334270474,173.01959677448016</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>-41.025588246969896,173.01914963671896</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>-41.02500512113546,173.018834427439</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F946"/>
+  <dimension ref="A1:F950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23136,6 +23136,102 @@
         <v>214.58</v>
       </c>
       <c r="F946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>220.79</v>
+      </c>
+      <c r="C947" t="n">
+        <v>222.38</v>
+      </c>
+      <c r="D947" t="n">
+        <v>221.38</v>
+      </c>
+      <c r="E947" t="n">
+        <v>213.83</v>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>219.76</v>
+      </c>
+      <c r="C948" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="D948" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="E948" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>218.72</v>
+      </c>
+      <c r="C949" t="n">
+        <v>220.84</v>
+      </c>
+      <c r="D949" t="n">
+        <v>220.01</v>
+      </c>
+      <c r="E949" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>218.13</v>
+      </c>
+      <c r="C950" t="n">
+        <v>220.72</v>
+      </c>
+      <c r="D950" t="n">
+        <v>220.15</v>
+      </c>
+      <c r="E950" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="F950" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23152,7 +23248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1074"/>
+  <dimension ref="A1:B1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33895,6 +33991,46 @@
       </c>
       <c r="B1074" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
@@ -34057,28 +34193,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1668602274841363</v>
+        <v>0.1677425523525391</v>
       </c>
       <c r="J2" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K2" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08894433994475248</v>
+        <v>0.09054668453239068</v>
       </c>
       <c r="M2" t="n">
-        <v>3.365144818909067</v>
+        <v>3.355799239323501</v>
       </c>
       <c r="N2" t="n">
-        <v>16.001672099895</v>
+        <v>15.9431628072848</v>
       </c>
       <c r="O2" t="n">
-        <v>4.000209007026383</v>
+        <v>3.992889030174116</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8661483941938</v>
+        <v>213.857063050163</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34129,28 +34265,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1193457409547001</v>
+        <v>0.1183786426658651</v>
       </c>
       <c r="J3" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K3" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06763802362948934</v>
+        <v>0.06717716000794582</v>
       </c>
       <c r="M3" t="n">
-        <v>2.893821504895812</v>
+        <v>2.886316940785267</v>
       </c>
       <c r="N3" t="n">
-        <v>11.01642304442266</v>
+        <v>10.97752343835294</v>
       </c>
       <c r="O3" t="n">
-        <v>3.319099734027686</v>
+        <v>3.313234588487954</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4290922168425</v>
+        <v>219.4390670378493</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34201,28 +34337,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.110041705451259</v>
+        <v>0.1066034657626951</v>
       </c>
       <c r="J4" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K4" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05557984437837649</v>
+        <v>0.05251614950805694</v>
       </c>
       <c r="M4" t="n">
-        <v>2.944438450326324</v>
+        <v>2.94892311465957</v>
       </c>
       <c r="N4" t="n">
-        <v>11.54504568797386</v>
+        <v>11.5664934979459</v>
       </c>
       <c r="O4" t="n">
-        <v>3.397800124782777</v>
+        <v>3.400954792105579</v>
       </c>
       <c r="P4" t="n">
-        <v>221.6813816014607</v>
+        <v>221.7168261669614</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34273,28 +34409,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0166718105859321</v>
+        <v>0.01338870411497536</v>
       </c>
       <c r="J5" t="n">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="K5" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001640880403046219</v>
+        <v>0.001061972195932848</v>
       </c>
       <c r="M5" t="n">
-        <v>2.538035597444958</v>
+        <v>2.545561706763538</v>
       </c>
       <c r="N5" t="n">
-        <v>9.457074088020464</v>
+        <v>9.480590936411572</v>
       </c>
       <c r="O5" t="n">
-        <v>3.075235615041629</v>
+        <v>3.079056825784736</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6921666101303</v>
+        <v>216.7260950834539</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34332,7 +34468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F946"/>
+  <dimension ref="A1:F950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64603,6 +64739,134 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>-41.026868426229704,173.02001659899733</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>-41.02622470408994,173.01958836285397</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>-41.02559173678451,173.01914063716998</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>-41.02500512102023,173.01882550627445</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>-41.02687276491112,173.02000576895</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>-41.02622672598133,173.01958331587784</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>-41.02559493920201,173.01913237875945</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>-41.0250051209693,173.01882158096205</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>-41.02687714571465,173.01999483375516</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>-41.026231190990686,173.01957217047112</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>-41.02559736154305,173.0191261320125</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>-41.02500512082974,173.01881087556455</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>-41.0268796309777,173.01998863013438</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>-41.026231696463384,173.01957090872688</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>-41.0255967867503,173.0191276142915</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>-41.02500512090741,173.0188168230076</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F950"/>
+  <dimension ref="A1:F954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23232,6 +23232,102 @@
         <v>213.1</v>
       </c>
       <c r="F950" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>217.3</v>
+      </c>
+      <c r="C951" t="n">
+        <v>219.82</v>
+      </c>
+      <c r="D951" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="E951" t="n">
+        <v>212.95</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>217.19</v>
+      </c>
+      <c r="C952" t="n">
+        <v>220</v>
+      </c>
+      <c r="D952" t="n">
+        <v>220.17</v>
+      </c>
+      <c r="E952" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="C953" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="D953" t="n">
+        <v>220.48</v>
+      </c>
+      <c r="E953" t="n">
+        <v>214.06</v>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>217.41</v>
+      </c>
+      <c r="C954" t="n">
+        <v>219.78</v>
+      </c>
+      <c r="D954" t="n">
+        <v>220.61</v>
+      </c>
+      <c r="E954" t="n">
+        <v>214.15</v>
+      </c>
+      <c r="F954" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23248,7 +23344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1078"/>
+  <dimension ref="A1:B1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34031,6 +34127,46 @@
       </c>
       <c r="B1078" t="n">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -34193,28 +34329,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1677425523525391</v>
+        <v>0.1669815315922519</v>
       </c>
       <c r="J2" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K2" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09054668453239068</v>
+        <v>0.09057045351598147</v>
       </c>
       <c r="M2" t="n">
-        <v>3.355799239323501</v>
+        <v>3.345424518210492</v>
       </c>
       <c r="N2" t="n">
-        <v>15.9431628072848</v>
+        <v>15.87986808386601</v>
       </c>
       <c r="O2" t="n">
-        <v>3.992889030174116</v>
+        <v>3.984955217297431</v>
       </c>
       <c r="P2" t="n">
-        <v>213.857063050163</v>
+        <v>213.8649375752873</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34265,28 +34401,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1183786426658651</v>
+        <v>0.116134412480711</v>
       </c>
       <c r="J3" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K3" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06717716000794582</v>
+        <v>0.06523738679981805</v>
       </c>
       <c r="M3" t="n">
-        <v>2.886316940785267</v>
+        <v>2.884974002909674</v>
       </c>
       <c r="N3" t="n">
-        <v>10.97752343835294</v>
+        <v>10.96109961428485</v>
       </c>
       <c r="O3" t="n">
-        <v>3.313234588487954</v>
+        <v>3.310755142604909</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4390670378493</v>
+        <v>219.4622909202991</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34337,28 +34473,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1066034657626951</v>
+        <v>0.1030049158293769</v>
       </c>
       <c r="J4" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K4" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05251614950805694</v>
+        <v>0.04934234909869895</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94892311465957</v>
+        <v>2.954208703250688</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5664934979459</v>
+        <v>11.59438511842837</v>
       </c>
       <c r="O4" t="n">
-        <v>3.400954792105579</v>
+        <v>3.405052880415864</v>
       </c>
       <c r="P4" t="n">
-        <v>221.7168261669614</v>
+        <v>221.7540626165987</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34409,28 +34545,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01338870411497536</v>
+        <v>0.010507739530281</v>
       </c>
       <c r="J5" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="K5" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001061972195932848</v>
+        <v>0.0006572635935958582</v>
       </c>
       <c r="M5" t="n">
-        <v>2.545561706763538</v>
+        <v>2.550988577993435</v>
       </c>
       <c r="N5" t="n">
-        <v>9.480590936411572</v>
+        <v>9.49026354647857</v>
       </c>
       <c r="O5" t="n">
-        <v>3.079056825784736</v>
+        <v>3.080627135256484</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7260950834539</v>
+        <v>216.7559786166753</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34468,7 +34604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F950"/>
+  <dimension ref="A1:F954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64867,6 +65003,134 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>-41.02688312719469,173.019979903006</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>-41.02623548750811,173.01956144564437</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>-41.02559805950566,173.0191243321023</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>-41.02500512088413,173.01881503877468</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>-41.02688359054869,173.01997874639858</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>-41.02623472929922,173.01956333826098</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>-41.02559670463706,173.01912782604563</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>-41.0250051209693,173.01882158096205</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>-41.026881021039976,173.01998516031236</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>-41.026234308072056,173.0195643897146</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>-41.02559543188156,173.01913110823472</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>-41.025005121055635,173.01882824209824</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>-41.026882663840674,173.01998105961346</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>-41.026235655998974,173.01956102506293</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>-41.02559489814538,173.01913248463651</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>-41.025005121069476,173.018829312638</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F954"/>
+  <dimension ref="A1:F960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23328,6 +23328,150 @@
         <v>214.15</v>
       </c>
       <c r="F954" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>216.58</v>
+      </c>
+      <c r="C955" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="D955" t="n">
+        <v>220.63</v>
+      </c>
+      <c r="E955" t="n">
+        <v>214.21</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>216.07</v>
+      </c>
+      <c r="C956" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="D956" t="n">
+        <v>220.84</v>
+      </c>
+      <c r="E956" t="n">
+        <v>214.61</v>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>214.69</v>
+      </c>
+      <c r="C957" t="n">
+        <v>219.14</v>
+      </c>
+      <c r="D957" t="n">
+        <v>220.69</v>
+      </c>
+      <c r="E957" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="C958" t="n">
+        <v>219.38</v>
+      </c>
+      <c r="D958" t="n">
+        <v>221.04</v>
+      </c>
+      <c r="E958" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="C959" t="n">
+        <v>218.23</v>
+      </c>
+      <c r="D959" t="n">
+        <v>219.96</v>
+      </c>
+      <c r="E959" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="C960" t="n">
+        <v>218.52</v>
+      </c>
+      <c r="D960" t="n">
+        <v>220.38</v>
+      </c>
+      <c r="E960" t="n">
+        <v>216.38</v>
+      </c>
+      <c r="F960" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23344,7 +23488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1082"/>
+  <dimension ref="A1:B1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34167,6 +34311,66 @@
       </c>
       <c r="B1082" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -34329,28 +34533,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1669815315922519</v>
+        <v>0.1631712649715463</v>
       </c>
       <c r="J2" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K2" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09057045351598147</v>
+        <v>0.08766865224273801</v>
       </c>
       <c r="M2" t="n">
-        <v>3.345424518210492</v>
+        <v>3.342918895214833</v>
       </c>
       <c r="N2" t="n">
-        <v>15.87986808386601</v>
+        <v>15.84181975396127</v>
       </c>
       <c r="O2" t="n">
-        <v>3.984955217297431</v>
+        <v>3.980178357054025</v>
       </c>
       <c r="P2" t="n">
-        <v>213.8649375752873</v>
+        <v>213.9045066648542</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34401,28 +34605,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116134412480711</v>
+        <v>0.1116803126273816</v>
       </c>
       <c r="J3" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K3" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06523738679981805</v>
+        <v>0.06102527812676783</v>
       </c>
       <c r="M3" t="n">
-        <v>2.884974002909674</v>
+        <v>2.888041831822598</v>
       </c>
       <c r="N3" t="n">
-        <v>10.96109961428485</v>
+        <v>10.9725309573343</v>
       </c>
       <c r="O3" t="n">
-        <v>3.310755142604909</v>
+        <v>3.31248108784553</v>
       </c>
       <c r="P3" t="n">
-        <v>219.4622909202991</v>
+        <v>219.5085405483266</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34473,28 +34677,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1030049158293769</v>
+        <v>0.09813314951799784</v>
       </c>
       <c r="J4" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K4" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04934234909869895</v>
+        <v>0.0452523625075345</v>
       </c>
       <c r="M4" t="n">
-        <v>2.954208703250688</v>
+        <v>2.959483579861246</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59438511842837</v>
+        <v>11.61684645784798</v>
       </c>
       <c r="O4" t="n">
-        <v>3.405052880415864</v>
+        <v>3.408349521080251</v>
       </c>
       <c r="P4" t="n">
-        <v>221.7540626165987</v>
+        <v>221.8046465448761</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34545,28 +34749,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.010507739530281</v>
+        <v>0.00833809992473448</v>
       </c>
       <c r="J5" t="n">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="K5" t="n">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006572635935958582</v>
+        <v>0.000418960043745642</v>
       </c>
       <c r="M5" t="n">
-        <v>2.550988577993435</v>
+        <v>2.547134809580807</v>
       </c>
       <c r="N5" t="n">
-        <v>9.49026354647857</v>
+        <v>9.452637081242287</v>
       </c>
       <c r="O5" t="n">
-        <v>3.080627135256484</v>
+        <v>3.074514121164885</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7559786166753</v>
+        <v>216.7785513385802</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34604,7 +34808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F954"/>
+  <dimension ref="A1:F960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65131,6 +65335,198 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>-41.02688616005707,173.0199723324843</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>-41.02623759364374,173.01955618837584</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>-41.02559481603212,173.01913269639064</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>-41.025005121078706,173.01883002633116</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>-41.02688830833428,173.019966970031</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>-41.02623759364374,173.01955618837584</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>-41.02559395384284,173.01913491980895</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>-41.02500512114005,173.0188347842856</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>-41.02689412131844,173.01995245986143</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>-41.0262383518525,173.01955429575912</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>-41.02559456969233,173.01913333165302</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>-41.025005121245435,173.01884299175703</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>-41.026894163441504,173.01995235471526</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>-41.026237340907464,173.0195568192481</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>-41.02559313271016,173.0191370373501</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>-41.02500512129562,173.01884691706942</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>-41.026894163441504,173.01995235471526</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>-41.02624218501857,173.0195447275293</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>-41.02559756682617,173.01912560262716</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>-41.02500512129562,173.01884691706942</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>-41.02689323673402,173.01995466793088</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>-41.02624096346024,173.01954777674553</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>-41.02559584244786,173.01913004946402</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>-41.0250051214092,173.018855838234</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F960"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23472,6 +23472,126 @@
         <v>216.38</v>
       </c>
       <c r="F960" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="C961" t="n">
+        <v>218.57</v>
+      </c>
+      <c r="D961" t="n">
+        <v>221</v>
+      </c>
+      <c r="E961" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>214.53</v>
+      </c>
+      <c r="C962" t="n">
+        <v>218.94</v>
+      </c>
+      <c r="D962" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="E962" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="C963" t="n">
+        <v>219.23</v>
+      </c>
+      <c r="D963" t="n">
+        <v>221.89</v>
+      </c>
+      <c r="E963" t="n">
+        <v>219.25</v>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>214.69</v>
+      </c>
+      <c r="C964" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="D964" t="n">
+        <v>222.51</v>
+      </c>
+      <c r="E964" t="n">
+        <v>220.03</v>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>214.97</v>
+      </c>
+      <c r="C965" t="n">
+        <v>219.51</v>
+      </c>
+      <c r="D965" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="E965" t="n">
+        <v>220.03</v>
+      </c>
+      <c r="F965" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23488,7 +23608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1088"/>
+  <dimension ref="A1:B1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34371,6 +34491,56 @@
       </c>
       <c r="B1088" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -34533,28 +34703,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1631712649715463</v>
+        <v>0.1593684183002679</v>
       </c>
       <c r="J2" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K2" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08766865224273801</v>
+        <v>0.08453499829636801</v>
       </c>
       <c r="M2" t="n">
-        <v>3.342918895214833</v>
+        <v>3.343956935919215</v>
       </c>
       <c r="N2" t="n">
-        <v>15.84181975396127</v>
+        <v>15.83012725498324</v>
       </c>
       <c r="O2" t="n">
-        <v>3.980178357054025</v>
+        <v>3.978709244841</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9045066648542</v>
+        <v>213.9441307982719</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34605,28 +34775,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1116803126273816</v>
+        <v>0.1082574247753548</v>
       </c>
       <c r="J3" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K3" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06102527812676783</v>
+        <v>0.05790947513342348</v>
       </c>
       <c r="M3" t="n">
-        <v>2.888041831822598</v>
+        <v>2.889123264228314</v>
       </c>
       <c r="N3" t="n">
-        <v>10.9725309573343</v>
+        <v>10.9731944380151</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31248108784553</v>
+        <v>3.312581234930715</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5085405483266</v>
+        <v>219.5442035147515</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34677,28 +34847,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09813314951799784</v>
+        <v>0.09559361538240199</v>
       </c>
       <c r="J4" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K4" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0452523625075345</v>
+        <v>0.04340621456496452</v>
       </c>
       <c r="M4" t="n">
-        <v>2.959483579861246</v>
+        <v>2.956426608735845</v>
       </c>
       <c r="N4" t="n">
-        <v>11.61684645784798</v>
+        <v>11.59065823040498</v>
       </c>
       <c r="O4" t="n">
-        <v>3.408349521080251</v>
+        <v>3.404505577966495</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8046465448761</v>
+        <v>221.8311002535976</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34749,28 +34919,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00833809992473448</v>
+        <v>0.01023307044123187</v>
       </c>
       <c r="J5" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="K5" t="n">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000418960043745642</v>
+        <v>0.0006367326995208034</v>
       </c>
       <c r="M5" t="n">
-        <v>2.547134809580807</v>
+        <v>2.542253943474696</v>
       </c>
       <c r="N5" t="n">
-        <v>9.452637081242287</v>
+        <v>9.428057627053697</v>
       </c>
       <c r="O5" t="n">
-        <v>3.074514121164885</v>
+        <v>3.070514228440197</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7785513385802</v>
+        <v>216.7587439540194</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34808,7 +34978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F960"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65527,6 +65697,166 @@
         </is>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>-41.02689492165671,173.01995046208427</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>-41.026240752846725,173.01954830247246</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>-41.025593296936705,173.01913661384188</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>-41.02500512153259,173.0188655920406</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>-41.026894795287504,173.01995077752278</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>-41.02623919430664,173.01955219285153</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>-41.02559165467123,173.01914084892408</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>-41.02500512160742,173.01887153948363</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>-41.026896185348605,173.01994730769917</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>-41.02623797274812,173.0195552420675</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>-41.025589642895824,173.01914603689949</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>-41.02500512183744,173.0188899765571</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>-41.02689412131844,173.01995245986143</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>-41.02623641420781,173.01955913244626</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>-41.025587097383756,173.0191526012761</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>-41.025005121952084,173.01889925456825</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>-41.02689294187252,173.01995540395401</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>-41.02623679331222,173.0195581861379</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>-41.02558500349452,173.01915800100485</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>-41.025005121952084,173.01889925456825</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F965"/>
+  <dimension ref="A1:F968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23592,6 +23592,78 @@
         <v>220.03</v>
       </c>
       <c r="F965" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>215.21</v>
+      </c>
+      <c r="C966" t="n">
+        <v>219.83</v>
+      </c>
+      <c r="D966" t="n">
+        <v>223.52</v>
+      </c>
+      <c r="E966" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>215.04</v>
+      </c>
+      <c r="C967" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="D967" t="n">
+        <v>223.84</v>
+      </c>
+      <c r="E967" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="C968" t="n">
+        <v>220.06</v>
+      </c>
+      <c r="D968" t="n">
+        <v>224.06</v>
+      </c>
+      <c r="E968" t="n">
+        <v>220.37</v>
+      </c>
+      <c r="F968" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23608,7 +23680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1093"/>
+  <dimension ref="A1:B1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34541,6 +34613,36 @@
       </c>
       <c r="B1093" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34703,28 +34805,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1593684183002679</v>
+        <v>0.1574763747958309</v>
       </c>
       <c r="J2" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K2" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08453499829636801</v>
+        <v>0.08309961132454224</v>
       </c>
       <c r="M2" t="n">
-        <v>3.343956935919215</v>
+        <v>3.342666669998297</v>
       </c>
       <c r="N2" t="n">
-        <v>15.83012725498324</v>
+        <v>15.81028317154032</v>
       </c>
       <c r="O2" t="n">
-        <v>3.978709244841</v>
+        <v>3.976214678754194</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9441307982719</v>
+        <v>213.963909368328</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34775,28 +34877,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1082574247753548</v>
+        <v>0.1066949010001283</v>
       </c>
       <c r="J3" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K3" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05790947513342348</v>
+        <v>0.05662166037139316</v>
       </c>
       <c r="M3" t="n">
-        <v>2.889123264228314</v>
+        <v>2.887499325248995</v>
       </c>
       <c r="N3" t="n">
-        <v>10.9731944380151</v>
+        <v>10.9591355013049</v>
       </c>
       <c r="O3" t="n">
-        <v>3.312581234930715</v>
+        <v>3.310458503184249</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5442035147515</v>
+        <v>219.560537179766</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34847,28 +34949,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09559361538240199</v>
+        <v>0.09522521390330842</v>
       </c>
       <c r="J4" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K4" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04340621456496452</v>
+        <v>0.04337362855766824</v>
       </c>
       <c r="M4" t="n">
-        <v>2.956426608735845</v>
+        <v>2.949020762759757</v>
       </c>
       <c r="N4" t="n">
-        <v>11.59065823040498</v>
+        <v>11.55596383199386</v>
       </c>
       <c r="O4" t="n">
-        <v>3.404505577966495</v>
+        <v>3.399406394062625</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8311002535976</v>
+        <v>221.83495077551</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34919,28 +35021,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01023307044123187</v>
+        <v>0.01232245105240014</v>
       </c>
       <c r="J5" t="n">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K5" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006367326995208034</v>
+        <v>0.0009260642880173364</v>
       </c>
       <c r="M5" t="n">
-        <v>2.542253943474696</v>
+        <v>2.543538103733336</v>
       </c>
       <c r="N5" t="n">
-        <v>9.428057627053697</v>
+        <v>9.434285007987137</v>
       </c>
       <c r="O5" t="n">
-        <v>3.070514228440197</v>
+        <v>3.071528122610493</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7587439540194</v>
+        <v>216.7368493374707</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34978,7 +35080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F965"/>
+  <dimension ref="A1:F968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65857,6 +65959,102 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>-41.02689193091882,173.01995792746186</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>-41.026235445385396,173.01956155078975</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>-41.02558295066167,173.01916329485624</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>-41.025005122020794,173.0189048451647</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>-41.02689264701103,173.01995613997713</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>-41.026235403262675,173.01956165593512</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>-41.025581636848536,173.01916668292094</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>-41.02500512200911,173.01890389357382</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>-41.02689197304189,173.01995782231572</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>-41.02623447656292,173.01956396913315</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>-41.025580733601934,173.0191690122154</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>-41.02500512200181,173.01890329882954</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
